--- a/research/traditional_assets/database/data/finland/finland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09765</v>
+        <v>0.080085</v>
       </c>
       <c r="E2">
-        <v>0.1675</v>
-      </c>
-      <c r="F2">
-        <v>0.03700000000000001</v>
+        <v>0.02999999999999997</v>
       </c>
       <c r="G2">
-        <v>0.08466864490603364</v>
+        <v>0.0491725768321513</v>
       </c>
       <c r="H2">
-        <v>0.006528189910979229</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006973293768545994</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.004382610158813473</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>10.769</v>
+        <v>12.575</v>
       </c>
       <c r="L2">
-        <v>0.05325914935707221</v>
+        <v>0.07432033096926716</v>
       </c>
       <c r="M2">
-        <v>9.368</v>
+        <v>12.796</v>
       </c>
       <c r="N2">
-        <v>0.03302079661614381</v>
+        <v>0.05654441007512152</v>
       </c>
       <c r="O2">
-        <v>0.8699043550933234</v>
+        <v>1.017574552683896</v>
       </c>
       <c r="P2">
-        <v>8.57</v>
+        <v>12.39</v>
       </c>
       <c r="Q2">
-        <v>0.03020796616143814</v>
+        <v>0.05475033141847106</v>
       </c>
       <c r="R2">
-        <v>0.7958027672021544</v>
+        <v>0.9852882703777336</v>
       </c>
       <c r="S2">
-        <v>0.798</v>
+        <v>0.4060000000000006</v>
       </c>
       <c r="T2">
-        <v>0.08518360375747225</v>
+        <v>0.03172866520787751</v>
       </c>
       <c r="U2">
-        <v>364.54</v>
+        <v>149.3</v>
       </c>
       <c r="V2">
-        <v>1.284948889672189</v>
+        <v>0.6597437030490499</v>
       </c>
       <c r="W2">
-        <v>0.02028018679119413</v>
+        <v>0.1341694951671906</v>
       </c>
       <c r="X2">
-        <v>0.02692791094739762</v>
+        <v>0.05562669323410519</v>
       </c>
       <c r="Y2">
-        <v>-0.006647724156203495</v>
+        <v>0.07854280193308538</v>
       </c>
       <c r="Z2">
-        <v>2.049255092733353</v>
+        <v>4.438614900314795</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02516008126411007</v>
+        <v>0.05134978171835317</v>
       </c>
       <c r="AC2">
-        <v>-0.02380751767292569</v>
+        <v>-0.05134978171835317</v>
       </c>
       <c r="AD2">
-        <v>179.42</v>
+        <v>102.59</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>179.42</v>
+        <v>102.59</v>
       </c>
       <c r="AG2">
-        <v>-185.12</v>
+        <v>-46.71000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.387415788564519</v>
+        <v>0.3119280002432425</v>
       </c>
       <c r="AI2">
-        <v>0.4031728911060178</v>
+        <v>0.3258998062200197</v>
       </c>
       <c r="AJ2">
-        <v>-1.877865692838304</v>
+        <v>-0.260092432763517</v>
       </c>
       <c r="AK2">
-        <v>-2.300198807157059</v>
+        <v>-0.2822527040908817</v>
       </c>
       <c r="AL2">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.3969999999999999</v>
-      </c>
-      <c r="AN2">
-        <v>89.71000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>1.165289256198347</v>
-      </c>
-      <c r="AP2">
-        <v>-92.56</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="AQ2">
-        <v>3.551637279596978</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fellow Finance Plc (HLSE:FELLOW)</t>
+          <t>United Bankers Oyj (HLSE:UNITED)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,113 +712,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.17</v>
+      </c>
+      <c r="E3">
+        <v>0.5479999999999999</v>
+      </c>
       <c r="G3">
-        <v>0.103125</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.103125</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.11015625</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.05507812499999999</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.251</v>
+        <v>11.9</v>
       </c>
       <c r="L3">
-        <v>-0.019609375</v>
+        <v>0.2474012474012474</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>9.096</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05674360573923892</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.7643697478991597</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>8.69</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05421085464753586</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.7302521008403361</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.4060000000000006</v>
+      </c>
+      <c r="T3">
+        <v>0.04463500439753744</v>
       </c>
       <c r="U3">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.1489177489177489</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.01619354838709677</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="X3">
-        <v>0.02692791094739762</v>
+        <v>0.04933220499856995</v>
       </c>
       <c r="Y3">
-        <v>-0.0431214593344944</v>
+        <v>0.2157012025738131</v>
       </c>
       <c r="Z3">
-        <v>0.5302402651201326</v>
+        <v>1.596945551128818</v>
       </c>
       <c r="AA3">
-        <v>0.0292046396023198</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.02516008126411007</v>
+        <v>0.04923464019276919</v>
       </c>
       <c r="AC3">
-        <v>0.004044558338209724</v>
+        <v>-0.04923464019276919</v>
       </c>
       <c r="AD3">
-        <v>10.8</v>
+        <v>2.09</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.8</v>
+        <v>2.09</v>
       </c>
       <c r="AG3">
-        <v>7.360000000000001</v>
+        <v>2.09</v>
       </c>
       <c r="AH3">
-        <v>0.3185840707964601</v>
+        <v>0.0128702506311965</v>
       </c>
       <c r="AI3">
-        <v>0.4014869888475837</v>
+        <v>0.04666220138423754</v>
       </c>
       <c r="AJ3">
-        <v>0.2416283650689429</v>
+        <v>0.0128702506311965</v>
       </c>
       <c r="AK3">
-        <v>0.3137254901960785</v>
+        <v>0.04666220138423754</v>
       </c>
       <c r="AL3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.187</v>
-      </c>
-      <c r="AN3">
-        <v>5.4</v>
-      </c>
-      <c r="AO3">
-        <v>1.165289256198347</v>
-      </c>
-      <c r="AP3">
-        <v>3.680000000000001</v>
-      </c>
-      <c r="AQ3">
-        <v>1.187868576242628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Bankers Oyj (HLSE:UNITED)</t>
+          <t>Multitude SE (XTRA:FRU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.129</v>
+        <v>-0.00983</v>
       </c>
       <c r="E4">
-        <v>0.584</v>
+        <v>-0.488</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.06870355078447564</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -868,218 +853,93 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7.98</v>
+        <v>0.675</v>
       </c>
       <c r="L4">
-        <v>0.1801354401805869</v>
+        <v>0.005573905862923205</v>
       </c>
       <c r="M4">
-        <v>7.088</v>
+        <v>3.7</v>
       </c>
       <c r="N4">
-        <v>0.04244311377245509</v>
+        <v>0.05606060606060606</v>
       </c>
       <c r="O4">
-        <v>0.8882205513784461</v>
+        <v>5.481481481481481</v>
       </c>
       <c r="P4">
-        <v>6.29</v>
+        <v>3.7</v>
       </c>
       <c r="Q4">
-        <v>0.03766467065868263</v>
+        <v>0.05606060606060606</v>
       </c>
       <c r="R4">
-        <v>0.788220551378446</v>
+        <v>5.481481481481481</v>
       </c>
       <c r="S4">
-        <v>0.798</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.1125846501128668</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>149.3</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>2.262121212121212</v>
       </c>
       <c r="W4">
-        <v>0.1927536231884058</v>
+        <v>0.003305582761998042</v>
       </c>
       <c r="X4">
-        <v>0.02386161644510624</v>
+        <v>0.06192118146964044</v>
       </c>
       <c r="Y4">
-        <v>0.1688920067432996</v>
+        <v>-0.05861559870764239</v>
       </c>
       <c r="Z4">
-        <v>1.645005569996287</v>
+        <v>15.1375</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02380751767292569</v>
+        <v>0.05346492324393715</v>
       </c>
       <c r="AC4">
-        <v>-0.02380751767292569</v>
+        <v>-0.05346492324393715</v>
       </c>
       <c r="AD4">
-        <v>3.72</v>
+        <v>100.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.72</v>
+        <v>100.5</v>
       </c>
       <c r="AG4">
-        <v>3.72</v>
+        <v>-48.80000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.02179006560449859</v>
+        <v>0.6036036036036037</v>
       </c>
       <c r="AI4">
-        <v>0.0758873929008568</v>
+        <v>0.3722222222222222</v>
       </c>
       <c r="AJ4">
-        <v>0.02179006560449859</v>
+        <v>-2.837209302325584</v>
       </c>
       <c r="AK4">
-        <v>0.0758873929008568</v>
+        <v>-0.4043082021541012</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Multitude SE (XTRA:FRU)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0663</v>
-      </c>
-      <c r="E5">
-        <v>-0.249</v>
-      </c>
-      <c r="F5">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="G5">
-        <v>0.1088904203997243</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>3.04</v>
-      </c>
-      <c r="L5">
-        <v>0.02095106822880772</v>
-      </c>
-      <c r="M5">
-        <v>2.28</v>
-      </c>
-      <c r="N5">
-        <v>0.02435897435897436</v>
-      </c>
-      <c r="O5">
-        <v>0.7499999999999999</v>
-      </c>
-      <c r="P5">
-        <v>2.28</v>
-      </c>
-      <c r="Q5">
-        <v>0.02435897435897436</v>
-      </c>
-      <c r="R5">
-        <v>0.7499999999999999</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>361.1</v>
-      </c>
-      <c r="V5">
-        <v>3.857905982905983</v>
-      </c>
-      <c r="W5">
-        <v>0.02028018679119413</v>
-      </c>
-      <c r="X5">
-        <v>0.03584064784365736</v>
-      </c>
-      <c r="Y5">
-        <v>-0.01556046105246323</v>
-      </c>
-      <c r="Z5">
-        <v>3.048319327731091</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.02897194128942366</v>
-      </c>
-      <c r="AC5">
-        <v>-0.02897194128942366</v>
-      </c>
-      <c r="AD5">
-        <v>164.9</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>164.9</v>
-      </c>
-      <c r="AG5">
-        <v>-196.2</v>
-      </c>
-      <c r="AH5">
-        <v>0.6379110251450677</v>
-      </c>
-      <c r="AI5">
-        <v>0.4467623950149011</v>
-      </c>
-      <c r="AJ5">
-        <v>1.912280701754386</v>
-      </c>
-      <c r="AK5">
-        <v>-24.52500000000009</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-0.79</v>
-      </c>
-      <c r="AQ5">
+        <v>-0.8080000000000001</v>
+      </c>
+      <c r="AQ4">
         <v>-0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/finland/finland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_financial_svcs_non_bank_insurance.xlsx
@@ -588,13 +588,16 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.080085</v>
+        <v>0.02855</v>
       </c>
       <c r="E2">
-        <v>0.02999999999999997</v>
+        <v>0.14555</v>
+      </c>
+      <c r="F2">
+        <v>0.42</v>
       </c>
       <c r="G2">
-        <v>0.0491725768321513</v>
+        <v>0.05564648117839607</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,91 +609,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>12.575</v>
+        <v>32.8</v>
       </c>
       <c r="L2">
-        <v>0.07432033096926716</v>
+        <v>0.1789416257501364</v>
       </c>
       <c r="M2">
-        <v>12.796</v>
+        <v>21.47</v>
       </c>
       <c r="N2">
-        <v>0.05654441007512152</v>
+        <v>0.07728581713462924</v>
       </c>
       <c r="O2">
-        <v>1.017574552683896</v>
+        <v>0.6545731707317073</v>
       </c>
       <c r="P2">
-        <v>12.39</v>
+        <v>17.58</v>
       </c>
       <c r="Q2">
-        <v>0.05475033141847106</v>
+        <v>0.0632829373650108</v>
       </c>
       <c r="R2">
-        <v>0.9852882703777336</v>
+        <v>0.5359756097560976</v>
       </c>
       <c r="S2">
-        <v>0.4060000000000006</v>
+        <v>3.890000000000001</v>
       </c>
       <c r="T2">
-        <v>0.03172866520787751</v>
+        <v>0.1811830461108524</v>
       </c>
       <c r="U2">
-        <v>149.3</v>
+        <v>176.8</v>
       </c>
       <c r="V2">
-        <v>0.6597437030490499</v>
+        <v>0.6364290856731463</v>
       </c>
       <c r="W2">
-        <v>0.1341694951671906</v>
+        <v>0.2157556828040951</v>
       </c>
       <c r="X2">
-        <v>0.05562669323410519</v>
+        <v>0.05394014888598492</v>
       </c>
       <c r="Y2">
-        <v>0.07854280193308538</v>
+        <v>0.1618155339181102</v>
       </c>
       <c r="Z2">
-        <v>4.438614900314795</v>
+        <v>1.230283911671925</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05134978171835317</v>
+        <v>0.05171981602149741</v>
       </c>
       <c r="AC2">
-        <v>-0.05134978171835317</v>
+        <v>-0.05171981602149741</v>
       </c>
       <c r="AD2">
-        <v>102.59</v>
+        <v>58.781</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>102.59</v>
+        <v>58.781</v>
       </c>
       <c r="AG2">
-        <v>-46.71000000000001</v>
+        <v>-118.019</v>
       </c>
       <c r="AH2">
-        <v>0.3119280002432425</v>
+        <v>0.1746414681755655</v>
       </c>
       <c r="AI2">
-        <v>0.3258998062200197</v>
+        <v>0.1952331764541768</v>
       </c>
       <c r="AJ2">
-        <v>-0.260092432763517</v>
+        <v>-0.7386297494695868</v>
       </c>
       <c r="AK2">
-        <v>-0.2822527040908817</v>
+        <v>-0.9496141807677763</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.8080000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.17</v>
+        <v>0.104</v>
       </c>
       <c r="E3">
-        <v>0.5479999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,34 +734,34 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>11.9</v>
+        <v>13.5</v>
       </c>
       <c r="L3">
-        <v>0.2474012474012474</v>
+        <v>0.2504638218923933</v>
       </c>
       <c r="M3">
-        <v>9.096</v>
+        <v>9.24</v>
       </c>
       <c r="N3">
-        <v>0.05674360573923892</v>
+        <v>0.05397196261682243</v>
       </c>
       <c r="O3">
-        <v>0.7643697478991597</v>
+        <v>0.6844444444444444</v>
       </c>
       <c r="P3">
-        <v>8.69</v>
+        <v>8.81</v>
       </c>
       <c r="Q3">
-        <v>0.05421085464753586</v>
+        <v>0.05146028037383178</v>
       </c>
       <c r="R3">
-        <v>0.7302521008403361</v>
+        <v>0.6525925925925926</v>
       </c>
       <c r="S3">
-        <v>0.4060000000000006</v>
+        <v>0.4299999999999997</v>
       </c>
       <c r="T3">
-        <v>0.04463500439753744</v>
+        <v>0.04653679653679651</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -767,49 +770,49 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2650334075723831</v>
+        <v>0.3176470588235294</v>
       </c>
       <c r="X3">
-        <v>0.04933220499856995</v>
+        <v>0.05126800526096235</v>
       </c>
       <c r="Y3">
-        <v>0.2157012025738131</v>
+        <v>0.266379053562567</v>
       </c>
       <c r="Z3">
-        <v>1.596945551128818</v>
+        <v>1.905266878755744</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04923464019276919</v>
+        <v>0.05120784495201392</v>
       </c>
       <c r="AC3">
-        <v>-0.04923464019276919</v>
+        <v>-0.05120784495201392</v>
       </c>
       <c r="AD3">
-        <v>2.09</v>
+        <v>0.881</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.09</v>
+        <v>0.881</v>
       </c>
       <c r="AG3">
-        <v>2.09</v>
+        <v>0.881</v>
       </c>
       <c r="AH3">
-        <v>0.0128702506311965</v>
+        <v>0.005119682010216119</v>
       </c>
       <c r="AI3">
-        <v>0.04666220138423754</v>
+        <v>0.01832324618872319</v>
       </c>
       <c r="AJ3">
-        <v>0.0128702506311965</v>
+        <v>0.005119682010216119</v>
       </c>
       <c r="AK3">
-        <v>0.04666220138423754</v>
+        <v>0.01832324618872319</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +838,16 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00983</v>
+        <v>-0.0469</v>
       </c>
       <c r="E4">
-        <v>-0.488</v>
+        <v>0.0171</v>
+      </c>
+      <c r="F4">
+        <v>0.42</v>
       </c>
       <c r="G4">
-        <v>0.06870355078447564</v>
+        <v>0.07882534775888717</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -853,91 +859,91 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.675</v>
+        <v>19.3</v>
       </c>
       <c r="L4">
-        <v>0.005573905862923205</v>
+        <v>0.1491499227202473</v>
       </c>
       <c r="M4">
-        <v>3.7</v>
+        <v>12.23</v>
       </c>
       <c r="N4">
-        <v>0.05606060606060606</v>
+        <v>0.1147279549718574</v>
       </c>
       <c r="O4">
-        <v>5.481481481481481</v>
+        <v>0.6336787564766839</v>
       </c>
       <c r="P4">
-        <v>3.7</v>
+        <v>8.77</v>
       </c>
       <c r="Q4">
-        <v>0.05606060606060606</v>
+        <v>0.0822701688555347</v>
       </c>
       <c r="R4">
-        <v>5.481481481481481</v>
+        <v>0.4544041450777201</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.460000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.2829108748977924</v>
       </c>
       <c r="U4">
-        <v>149.3</v>
+        <v>176.8</v>
       </c>
       <c r="V4">
-        <v>2.262121212121212</v>
+        <v>1.658536585365854</v>
       </c>
       <c r="W4">
-        <v>0.003305582761998042</v>
+        <v>0.1138643067846608</v>
       </c>
       <c r="X4">
-        <v>0.06192118146964044</v>
+        <v>0.05661229251100749</v>
       </c>
       <c r="Y4">
-        <v>-0.05861559870764239</v>
+        <v>0.05725201427365328</v>
       </c>
       <c r="Z4">
-        <v>15.1375</v>
+        <v>1.072079536039768</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05346492324393715</v>
+        <v>0.0522317870909809</v>
       </c>
       <c r="AC4">
-        <v>-0.05346492324393715</v>
+        <v>-0.0522317870909809</v>
       </c>
       <c r="AD4">
-        <v>100.5</v>
+        <v>57.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>100.5</v>
+        <v>57.9</v>
       </c>
       <c r="AG4">
-        <v>-48.80000000000001</v>
+        <v>-118.9</v>
       </c>
       <c r="AH4">
-        <v>0.6036036036036037</v>
+        <v>0.3519756838905775</v>
       </c>
       <c r="AI4">
-        <v>0.3722222222222222</v>
+        <v>0.2288537549407114</v>
       </c>
       <c r="AJ4">
-        <v>-2.837209302325584</v>
+        <v>9.666666666666659</v>
       </c>
       <c r="AK4">
-        <v>-0.4043082021541012</v>
+        <v>-1.560367454068242</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.8080000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
